--- a/Result/profitability/4506.xlsx
+++ b/Result/profitability/4506.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>1.44875</v>
+        <v>1.5675</v>
       </c>
       <c r="N2" t="n">
-        <v>29.77125</v>
+        <v>30.11375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.26875</v>
+        <v>1.39125</v>
       </c>
       <c r="N3" t="n">
-        <v>27.935</v>
+        <v>28.92375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12125</v>
+        <v>1.20375</v>
       </c>
       <c r="N4" t="n">
-        <v>26.71</v>
+        <v>26.80625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9075</v>
+        <v>1.005</v>
       </c>
       <c r="N5" t="n">
-        <v>25.6375</v>
+        <v>25.8925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7224999999999999</v>
+        <v>0.7875</v>
       </c>
       <c r="N6" t="n">
-        <v>23.57625</v>
+        <v>23.93125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.49875</v>
+        <v>0.60875</v>
       </c>
       <c r="N7" t="n">
-        <v>22.9925</v>
+        <v>23.0775</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3462500000000001</v>
+        <v>0.375</v>
       </c>
       <c r="N8" t="n">
-        <v>21.825</v>
+        <v>21.90375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1576</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1038</v>
+      </c>
+      <c r="E75" t="n">
+        <v>539</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>367</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.28%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>120</v>
+      </c>
+      <c r="J75" t="n">
+        <v>488</v>
+      </c>
+      <c r="K75" t="n">
+        <v>415</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.715</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.95875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1090047393364928</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6299999999999955</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01878914405010423</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4999999999999998</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.039999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.06351183063511834</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
